--- a/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>WTMA</t>
   </si>
@@ -656,56 +656,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,8 +725,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -768,8 +772,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -812,8 +819,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -856,8 +866,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +887,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,8 +932,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -962,8 +979,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1006,8 +1026,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,8 +1073,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1065,32 +1091,33 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1109,8 +1136,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1118,23 +1148,23 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,8 +1183,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1171,8 +1204,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1180,22 +1214,22 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1215,8 +1249,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,23 +1261,23 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,8 +1296,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1303,32 +1343,35 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,25 +1390,28 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>100</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1382,8 +1428,8 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1391,8 +1437,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1435,32 +1484,35 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-800</v>
       </c>
       <c r="G26" s="3">
         <v>-800</v>
       </c>
       <c r="H26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1479,32 +1531,35 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-800</v>
       </c>
       <c r="G27" s="3">
         <v>-800</v>
       </c>
       <c r="H27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1523,8 +1578,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1567,8 +1625,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1672,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1655,8 +1719,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1699,8 +1766,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1708,22 +1778,22 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1743,32 +1813,35 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-800</v>
       </c>
       <c r="G33" s="3">
         <v>-800</v>
       </c>
       <c r="H33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1787,8 +1860,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1831,32 +1907,35 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-800</v>
       </c>
       <c r="G35" s="3">
         <v>-800</v>
       </c>
       <c r="H35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,37 +1954,40 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1924,8 +2006,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1942,8 +2027,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1960,32 +2046,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2004,8 +2091,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2048,17 +2138,20 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2074,8 +2167,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2092,8 +2185,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2136,32 +2232,35 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,32 +2279,35 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3">
         <v>200</v>
       </c>
       <c r="F46" s="3">
+        <v>200</v>
+      </c>
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2224,32 +2326,35 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E47" s="3">
         <v>38900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>80600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>79600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>78500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>77400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>77300</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2268,8 +2373,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2312,8 +2420,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2356,8 +2467,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2400,8 +2514,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2444,22 +2561,25 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>200</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2473,8 +2593,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2488,8 +2608,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2532,32 +2655,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>79000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2576,8 +2702,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2594,8 +2723,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2612,31 +2742,32 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="E57" s="3">
         <v>2600</v>
       </c>
       <c r="F57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2656,26 +2787,29 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,8 +2825,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2700,31 +2834,34 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2744,32 +2881,35 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E60" s="3">
         <v>5700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2788,8 +2928,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2832,8 +2975,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2855,8 +3001,8 @@
       <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>2700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2876,8 +3022,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2920,8 +3069,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2964,8 +3116,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3008,32 +3163,35 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E66" s="3">
         <v>8400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3210,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3070,8 +3231,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3114,8 +3276,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3158,8 +3323,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3202,8 +3370,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3246,32 +3417,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3290,8 +3464,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3334,8 +3511,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3378,8 +3558,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3422,32 +3605,35 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>30700</v>
+        <v>14600</v>
       </c>
       <c r="E76" s="3">
         <v>30700</v>
       </c>
       <c r="F76" s="3">
+        <v>30700</v>
+      </c>
+      <c r="G76" s="3">
         <v>73600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>75200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3652,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3510,37 +3699,40 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3559,32 +3751,35 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-800</v>
       </c>
       <c r="G81" s="3">
         <v>-800</v>
       </c>
       <c r="H81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3603,8 +3798,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3621,8 +3819,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3665,8 +3864,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3709,8 +3911,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3753,8 +3958,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3797,8 +4005,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3841,8 +4052,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3885,32 +4099,35 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,8 +4146,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3947,8 +4167,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3991,8 +4212,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4035,8 +4259,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4079,32 +4306,35 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>42200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4353,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4141,8 +4374,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4185,8 +4419,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4229,8 +4466,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4273,8 +4513,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4317,32 +4560,35 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>800</v>
       </c>
       <c r="G100" s="3">
         <v>800</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,8 +4607,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4405,32 +4654,35 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,6 +4699,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>WTMA</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,8 +729,14 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +782,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,8 +835,14 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,8 +888,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +913,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,8 +962,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,8 +1015,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,8 +1068,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1076,8 +1121,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,38 +1143,40 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>300</v>
+      </c>
+      <c r="F17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,8 +1192,14 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,29 +1207,29 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,8 +1245,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,8 +1270,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1214,28 +1281,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>500</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1252,8 +1319,14 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1261,29 +1334,29 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
       </c>
       <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,8 +1372,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,8 +1425,14 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1355,29 +1440,29 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,31 +1478,37 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1431,17 +1522,23 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,38 +1584,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1534,38 +1637,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1690,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1743,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1796,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1849,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,8 +1902,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1778,28 +1917,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1816,38 +1955,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,8 +2008,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,38 +2061,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,43 +2114,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2172,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2197,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,13 +2218,15 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -2062,23 +2235,23 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2267,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,23 +2320,29 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2170,11 +2355,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2188,8 +2373,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2235,8 +2426,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2244,29 +2441,29 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2282,38 +2479,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
         <v>100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,38 +2532,44 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F47" s="3">
         <v>39600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>38900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>80600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>79600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>78500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>77400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>77300</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2376,8 +2585,14 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2423,8 +2638,14 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2470,8 +2691,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2744,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,8 +2797,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2573,19 +2812,19 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>200</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2596,11 +2835,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2611,8 +2850,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,38 +2903,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F54" s="3">
         <v>40000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>39100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>81000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>80200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>79000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>78300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>78400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,8 +2956,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2981,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,37 +3002,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2790,32 +3051,38 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2828,47 +3095,53 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17100</v>
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
         <v>1000</v>
       </c>
       <c r="F59" s="3">
+        <v>17100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="3">
         <v>43400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,38 +3157,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F60" s="3">
         <v>22700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>47600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,8 +3210,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2978,8 +3263,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3004,11 +3295,11 @@
       <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2700</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -3025,8 +3316,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3369,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3422,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,38 +3475,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F66" s="3">
         <v>25400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>50300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3213,8 +3528,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3553,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3602,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3655,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3708,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,38 +3761,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-7600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-5900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-3900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-2100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3814,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3867,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3920,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,38 +3973,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E76" s="3">
         <v>14600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="G76" s="3">
         <v>30700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>30700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>73600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>74400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>75200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>75400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3655,8 +4026,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,43 +4079,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,38 +4137,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,8 +4190,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,8 +4215,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3867,8 +4264,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4317,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4370,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4423,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4476,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,38 +4529,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-42800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>42500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4149,8 +4582,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,8 +4607,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4215,8 +4656,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4709,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,38 +4762,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>42200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4356,8 +4815,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4840,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4422,8 +4889,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4942,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4995,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,38 +5048,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-42500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4610,8 +5101,14 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4657,38 +5154,44 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,6 +5205,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WTMA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>WTMA</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,8 +736,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,8 +792,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -841,8 +848,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,8 +904,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -915,8 +928,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -968,8 +982,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1021,8 +1038,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1074,8 +1094,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1127,8 +1150,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1145,8 +1171,9 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1157,29 +1184,29 @@
         <v>300</v>
       </c>
       <c r="F17" s="3">
+        <v>300</v>
+      </c>
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1198,8 +1225,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1210,29 +1240,29 @@
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,8 +1281,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1272,8 +1305,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1284,28 +1318,28 @@
         <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
         <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1325,8 +1359,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1334,32 +1371,32 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1415,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,8 +1471,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1440,32 +1483,32 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,8 +1527,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1496,22 +1542,22 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>100</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1528,8 +1574,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1537,8 +1583,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1590,8 +1639,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1599,32 +1651,32 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-800</v>
       </c>
       <c r="J26" s="3">
         <v>-800</v>
       </c>
       <c r="K26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1643,8 +1695,11 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1652,32 +1707,32 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-800</v>
       </c>
       <c r="J27" s="3">
         <v>-800</v>
       </c>
       <c r="K27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,8 +1751,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1749,8 +1807,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1802,8 +1863,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1855,8 +1919,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1908,8 +1975,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1920,28 +1990,28 @@
         <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
         <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1961,8 +2031,11 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1970,32 +2043,32 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-800</v>
       </c>
       <c r="J33" s="3">
         <v>-800</v>
       </c>
       <c r="K33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,8 +2087,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2067,8 +2143,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2076,32 +2155,32 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-800</v>
       </c>
       <c r="J35" s="3">
         <v>-800</v>
       </c>
       <c r="K35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,46 +2199,49 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2178,8 +2260,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2199,8 +2284,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2220,8 +2306,9 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2232,29 +2319,29 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2360,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2326,8 +2416,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2340,12 +2433,12 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,8 +2454,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2379,8 +2472,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2432,8 +2528,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2447,26 +2546,26 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,8 +2584,11 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2497,29 +2599,29 @@
         <v>0</v>
       </c>
       <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
         <v>100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>200</v>
       </c>
       <c r="H46" s="3">
         <v>200</v>
       </c>
       <c r="I46" s="3">
+        <v>200</v>
+      </c>
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1200</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,41 +2640,44 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E47" s="3">
         <v>24000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>23800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>38900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>80600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>79600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>78500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>77400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>77300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,8 +2696,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2644,8 +2752,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2697,8 +2808,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2750,8 +2864,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2803,8 +2920,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2818,16 +2938,16 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>200</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2841,8 +2961,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2856,8 +2976,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2909,41 +3032,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E54" s="3">
         <v>24200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>40000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>81000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>80200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3088,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2983,8 +3112,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3004,40 +3134,41 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
-      </c>
-      <c r="E57" s="3">
-        <v>2800</v>
       </c>
       <c r="F57" s="3">
         <v>2800</v>
       </c>
       <c r="G57" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="H57" s="3">
         <v>2600</v>
       </c>
       <c r="I57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -3057,35 +3188,38 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2800</v>
       </c>
       <c r="F58" s="3">
         <v>2800</v>
       </c>
       <c r="G58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,8 +3235,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3110,40 +3244,43 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>43400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>300</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>300</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -3163,41 +3300,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3356,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3269,8 +3412,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3301,8 +3447,8 @@
       <c r="L62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>2700</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3322,8 +3468,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3375,8 +3524,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3428,8 +3580,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3481,41 +3636,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E66" s="3">
         <v>9700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3692,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3555,8 +3716,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3608,8 +3770,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3661,8 +3826,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3714,8 +3882,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3767,41 +3938,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3820,8 +3994,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3873,8 +4050,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3926,8 +4106,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3979,41 +4162,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>14500</v>
-      </c>
-      <c r="E76" s="3">
-        <v>14600</v>
       </c>
       <c r="F76" s="3">
         <v>14600</v>
       </c>
       <c r="G76" s="3">
-        <v>30700</v>
+        <v>14600</v>
       </c>
       <c r="H76" s="3">
         <v>30700</v>
       </c>
       <c r="I76" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J76" s="3">
         <v>73600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>75200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>75400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4032,8 +4218,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4085,46 +4274,49 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4143,8 +4335,11 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4152,32 +4347,32 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-800</v>
       </c>
       <c r="J81" s="3">
         <v>-800</v>
       </c>
       <c r="K81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,8 +4391,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4217,8 +4415,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4270,8 +4469,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4323,8 +4525,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4376,8 +4581,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4429,8 +4637,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4482,8 +4693,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4535,41 +4749,44 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>42500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4588,8 +4805,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4609,8 +4829,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4662,8 +4883,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4715,8 +4939,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4768,8 +4995,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4777,32 +5007,32 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>16200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>42200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +5051,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4842,8 +5075,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4895,8 +5129,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4948,8 +5185,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5001,8 +5241,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5054,41 +5297,44 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>800</v>
       </c>
       <c r="J100" s="3">
         <v>800</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,8 +5353,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5160,8 +5409,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5169,32 +5421,32 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5211,6 +5463,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
